--- a/database/event/4932/event_4932_evp_summary.xlsx
+++ b/database/event/4932/event_4932_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.0391</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1279</v>
+        <v>3.0563</v>
       </c>
       <c r="E2" t="n">
         <v>8.7857</v>
@@ -548,7 +548,7 @@
         <v>3.8575</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9683</v>
+        <v>2.8989</v>
       </c>
       <c r="E3" t="n">
         <v>8.390599999999999</v>
@@ -594,7 +594,7 @@
         <v>3.1666</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3612</v>
+        <v>2.3002</v>
       </c>
       <c r="E4" t="n">
         <v>6.8879</v>
@@ -640,7 +640,7 @@
         <v>3.0632</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2703</v>
+        <v>2.2106</v>
       </c>
       <c r="E5" t="n">
         <v>6.663</v>
@@ -686,7 +686,7 @@
         <v>2.6299</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8896</v>
+        <v>1.8351</v>
       </c>
       <c r="E6" t="n">
         <v>5.7205</v>
@@ -732,7 +732,7 @@
         <v>2.5282</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8002</v>
+        <v>1.747</v>
       </c>
       <c r="E7" t="n">
         <v>5.4992</v>
@@ -778,7 +778,7 @@
         <v>2.369</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6603</v>
+        <v>1.609</v>
       </c>
       <c r="E8" t="n">
         <v>5.153</v>
@@ -824,7 +824,7 @@
         <v>2.19</v>
       </c>
       <c r="D9" t="n">
-        <v>1.503</v>
+        <v>1.4539</v>
       </c>
       <c r="E9" t="n">
         <v>4.7635</v>
@@ -870,7 +870,7 @@
         <v>2.1504</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4682</v>
+        <v>1.4196</v>
       </c>
       <c r="E10" t="n">
         <v>4.6774</v>
@@ -916,7 +916,7 @@
         <v>2.0878</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4132</v>
+        <v>1.3653</v>
       </c>
       <c r="E11" t="n">
         <v>4.5413</v>
@@ -962,7 +962,7 @@
         <v>2.0241</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3572</v>
+        <v>1.3101</v>
       </c>
       <c r="E12" t="n">
         <v>4.4027</v>
@@ -1008,7 +1008,7 @@
         <v>1.9152</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2616</v>
+        <v>1.2158</v>
       </c>
       <c r="E13" t="n">
         <v>4.1659</v>
@@ -1054,7 +1054,7 @@
         <v>1.6902</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0638</v>
+        <v>1.0208</v>
       </c>
       <c r="E14" t="n">
         <v>3.6764</v>
@@ -1100,7 +1100,7 @@
         <v>1.6717</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0476</v>
+        <v>1.0048</v>
       </c>
       <c r="E15" t="n">
         <v>3.6362</v>
@@ -1146,7 +1146,7 @@
         <v>1.6709</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0469</v>
+        <v>1.004</v>
       </c>
       <c r="E16" t="n">
         <v>3.6344</v>
@@ -1192,7 +1192,7 @@
         <v>1.6592</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0366</v>
+        <v>0.9939</v>
       </c>
       <c r="E17" t="n">
         <v>3.609</v>
@@ -1238,7 +1238,7 @@
         <v>1.49</v>
       </c>
       <c r="D18" t="n">
-        <v>0.888</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>3.2411</v>
@@ -1284,7 +1284,7 @@
         <v>1.4642</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8652</v>
+        <v>0.8249</v>
       </c>
       <c r="E19" t="n">
         <v>3.1848</v>
@@ -1330,7 +1330,7 @@
         <v>1.3125</v>
       </c>
       <c r="D20" t="n">
-        <v>0.732</v>
+        <v>0.6935</v>
       </c>
       <c r="E20" t="n">
         <v>2.855</v>
@@ -1376,7 +1376,7 @@
         <v>1.2971</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7185</v>
+        <v>0.6802</v>
       </c>
       <c r="E21" t="n">
         <v>2.8215</v>
@@ -1422,7 +1422,7 @@
         <v>1.2925</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7143</v>
+        <v>0.6761</v>
       </c>
       <c r="E22" t="n">
         <v>2.8113</v>
@@ -1468,7 +1468,7 @@
         <v>1.2728</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6591</v>
       </c>
       <c r="E23" t="n">
         <v>2.7686</v>
@@ -1514,7 +1514,7 @@
         <v>1.2076</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6398</v>
+        <v>0.6026</v>
       </c>
       <c r="E24" t="n">
         <v>2.6267</v>
@@ -1560,7 +1560,7 @@
         <v>1.1583</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5965</v>
+        <v>0.5599</v>
       </c>
       <c r="E25" t="n">
         <v>2.5195</v>
@@ -1606,7 +1606,7 @@
         <v>1.1396</v>
       </c>
       <c r="D26" t="n">
-        <v>0.58</v>
+        <v>0.5436</v>
       </c>
       <c r="E26" t="n">
         <v>2.4788</v>
@@ -1652,7 +1652,7 @@
         <v>1.1277</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5696</v>
+        <v>0.5334</v>
       </c>
       <c r="E27" t="n">
         <v>2.453</v>
@@ -1698,7 +1698,7 @@
         <v>0.9539</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4168</v>
+        <v>0.3827</v>
       </c>
       <c r="E28" t="n">
         <v>2.0748</v>
@@ -1744,7 +1744,7 @@
         <v>0.8577</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3323</v>
+        <v>0.2994</v>
       </c>
       <c r="E29" t="n">
         <v>1.8657</v>
@@ -1790,7 +1790,7 @@
         <v>0.8008</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2823</v>
+        <v>0.2501</v>
       </c>
       <c r="E30" t="n">
         <v>1.7419</v>
@@ -1836,7 +1836,7 @@
         <v>0.7886</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2716</v>
+        <v>0.2395</v>
       </c>
       <c r="E31" t="n">
         <v>1.7154</v>
@@ -1882,7 +1882,7 @@
         <v>0.721</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2122</v>
+        <v>0.1809</v>
       </c>
       <c r="E32" t="n">
         <v>1.5682</v>
@@ -1928,7 +1928,7 @@
         <v>0.6979</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1919</v>
+        <v>0.1609</v>
       </c>
       <c r="E33" t="n">
         <v>1.518</v>
@@ -1974,7 +1974,7 @@
         <v>0.6561</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1552</v>
+        <v>0.1247</v>
       </c>
       <c r="E34" t="n">
         <v>1.4272</v>
@@ -2020,7 +2020,7 @@
         <v>0.5991</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1051</v>
+        <v>0.0752</v>
       </c>
       <c r="E35" t="n">
         <v>1.3031</v>
@@ -2066,7 +2066,7 @@
         <v>0.5465</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0589</v>
+        <v>0.0297</v>
       </c>
       <c r="E36" t="n">
         <v>1.1888</v>
@@ -2112,7 +2112,7 @@
         <v>0.378</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0892</v>
+        <v>-0.1163</v>
       </c>
       <c r="E37" t="n">
         <v>0.8223</v>
@@ -2158,7 +2158,7 @@
         <v>0.3386</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1238</v>
+        <v>-0.1504</v>
       </c>
       <c r="E38" t="n">
         <v>0.7366</v>
@@ -2204,7 +2204,7 @@
         <v>0.2997</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.158</v>
+        <v>-0.1842</v>
       </c>
       <c r="E39" t="n">
         <v>0.6518</v>
@@ -2250,7 +2250,7 @@
         <v>0.2336</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2161</v>
+        <v>-0.2414</v>
       </c>
       <c r="E40" t="n">
         <v>0.5082</v>
@@ -2296,7 +2296,7 @@
         <v>0.2121</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.235</v>
+        <v>-0.2601</v>
       </c>
       <c r="E41" t="n">
         <v>0.4614</v>
@@ -2342,7 +2342,7 @@
         <v>0.182</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2614</v>
+        <v>-0.2862</v>
       </c>
       <c r="E42" t="n">
         <v>0.3959</v>
@@ -2388,7 +2388,7 @@
         <v>0.1557</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2846</v>
+        <v>-0.309</v>
       </c>
       <c r="E43" t="n">
         <v>0.3386</v>
@@ -2434,7 +2434,7 @@
         <v>0.1541</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.286</v>
+        <v>-0.3104</v>
       </c>
       <c r="E44" t="n">
         <v>0.3351</v>
@@ -2480,7 +2480,7 @@
         <v>0.1323</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3051</v>
+        <v>-0.3293</v>
       </c>
       <c r="E45" t="n">
         <v>0.2878</v>
@@ -2526,7 +2526,7 @@
         <v>0.0867</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3452</v>
+        <v>-0.3688</v>
       </c>
       <c r="E46" t="n">
         <v>0.1885</v>
@@ -2572,7 +2572,7 @@
         <v>0.0527</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.375</v>
+        <v>-0.3982</v>
       </c>
       <c r="E47" t="n">
         <v>0.1147</v>
@@ -2618,7 +2618,7 @@
         <v>0.0372</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3886</v>
+        <v>-0.4116</v>
       </c>
       <c r="E48" t="n">
         <v>0.081</v>
@@ -2664,7 +2664,7 @@
         <v>0.0336</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3919</v>
+        <v>-0.4148</v>
       </c>
       <c r="E49" t="n">
         <v>0.073</v>
@@ -2710,7 +2710,7 @@
         <v>0.0267</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3979</v>
+        <v>-0.4208</v>
       </c>
       <c r="E50" t="n">
         <v>0.0581</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0601</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4742</v>
+        <v>-0.496</v>
       </c>
       <c r="E51" t="n">
         <v>-0.1308</v>
@@ -2802,7 +2802,7 @@
         <v>-0.06950000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4824</v>
+        <v>-0.5041</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1512</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1037</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5125</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2256</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1132</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5208</v>
+        <v>-0.542</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2462</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2012</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5981</v>
+        <v>-0.6183</v>
       </c>
       <c r="E55" t="n">
         <v>-0.4376</v>
@@ -2986,7 +2986,7 @@
         <v>-0.212</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6077</v>
+        <v>-0.6277</v>
       </c>
       <c r="E56" t="n">
         <v>-0.4612</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2451</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6368</v>
+        <v>-0.6563</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5332</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3019</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6866</v>
+        <v>-0.7055</v>
       </c>
       <c r="E58" t="n">
         <v>-0.6566</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3043</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6887</v>
+        <v>-0.7076</v>
       </c>
       <c r="E59" t="n">
         <v>-0.6618000000000001</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3147</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6979</v>
+        <v>-0.7167</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6846</v>
@@ -3216,7 +3216,7 @@
         <v>-0.319</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7016</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6938</v>
@@ -3262,7 +3262,7 @@
         <v>-0.346</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7254</v>
+        <v>-0.7437</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7526</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4295</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7988</v>
+        <v>-0.8161</v>
       </c>
       <c r="E63" t="n">
         <v>-0.9343</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4995</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8603</v>
+        <v>-0.8768</v>
       </c>
       <c r="E64" t="n">
         <v>-1.0866</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5184</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8769</v>
+        <v>-0.8932</v>
       </c>
       <c r="E65" t="n">
         <v>-1.1277</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5474</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9023</v>
+        <v>-0.9182</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1906</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5504</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.905</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="E67" t="n">
         <v>-1.1972</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5679</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9204</v>
+        <v>-0.9361</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2353</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7177</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0521</v>
+        <v>-1.0659</v>
       </c>
       <c r="E69" t="n">
         <v>-1.5612</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7385</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0703</v>
+        <v>-1.0839</v>
       </c>
       <c r="E70" t="n">
         <v>-1.6064</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7495000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.08</v>
+        <v>-1.0934</v>
       </c>
       <c r="E71" t="n">
         <v>-1.6303</v>
@@ -3722,7 +3722,7 @@
         <v>-0.7895</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1151</v>
+        <v>-1.128</v>
       </c>
       <c r="E72" t="n">
         <v>-1.7172</v>
@@ -3768,7 +3768,7 @@
         <v>-0.7935</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1186</v>
+        <v>-1.1315</v>
       </c>
       <c r="E73" t="n">
         <v>-1.7259</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8147</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1373</v>
+        <v>-1.15</v>
       </c>
       <c r="E74" t="n">
         <v>-1.7722</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8199</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1419</v>
+        <v>-1.1545</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7835</v>
@@ -3906,7 +3906,7 @@
         <v>-0.8244</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1457</v>
+        <v>-1.1583</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7931</v>
@@ -3952,7 +3952,7 @@
         <v>-0.8855</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1995</v>
+        <v>-1.2113</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9261</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2122</v>
+        <v>-1.2239</v>
       </c>
       <c r="E78" t="n">
         <v>-1.9577</v>
@@ -4044,7 +4044,7 @@
         <v>-0.9195</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E79" t="n">
         <v>-2</v>
@@ -4090,7 +4090,7 @@
         <v>-0.9397</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2471</v>
+        <v>-1.2583</v>
       </c>
       <c r="E80" t="n">
         <v>-2.0441</v>
@@ -4136,7 +4136,7 @@
         <v>-1.0506</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3445</v>
+        <v>-1.3543</v>
       </c>
       <c r="E81" t="n">
         <v>-2.2852</v>
